--- a/assets/constructions/examples/ctd_tc_head.xlsx
+++ b/assets/constructions/examples/ctd_tc_head.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ctd" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="ctd" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AG6"/>
+  <dimension ref="A1:AK6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -594,6 +594,26 @@
           <t>releasepack</t>
         </is>
       </c>
+      <c r="AH1" s="1" t="inlineStr">
+        <is>
+          <t>lcs</t>
+        </is>
+      </c>
+      <c r="AI1" s="1" t="inlineStr">
+        <is>
+          <t>pricevalue</t>
+        </is>
+      </c>
+      <c r="AJ1" s="1" t="inlineStr">
+        <is>
+          <t>pricecurrency</t>
+        </is>
+      </c>
+      <c r="AK1" s="1" t="inlineStr">
+        <is>
+          <t>pricevalue_rub</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -603,7 +623,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>AVH32 SDNC R-11</t>
+          <t>AVH40 DCLN L-12</t>
         </is>
       </c>
       <c r="C2" t="inlineStr"/>
@@ -615,28 +635,28 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>D</t>
         </is>
       </c>
       <c r="G2" t="n">
-        <v>62.3</v>
+        <v>95</v>
       </c>
       <c r="H2" t="n">
-        <v>37.7</v>
+        <v>-5</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>DC..11T3..</t>
+          <t>CN..1204..</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>PALB_AVH:32</t>
+          <t>PALB_AVH:40</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>ISO_DC11T3H</t>
+          <t>ISO_CN1204H</t>
         </is>
       </c>
       <c r="L2" t="n">
@@ -644,24 +664,24 @@
       </c>
       <c r="M2" t="inlineStr"/>
       <c r="N2" t="n">
+        <v>50</v>
+      </c>
+      <c r="O2" t="n">
         <v>40</v>
-      </c>
-      <c r="O2" t="n">
-        <v>32</v>
       </c>
       <c r="P2" t="inlineStr"/>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>Z</t>
+          <t>ZX</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>L</t>
         </is>
       </c>
       <c r="S2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="T2" t="n">
         <v>0</v>
@@ -674,10 +694,10 @@
         <v>0</v>
       </c>
       <c r="X2" t="n">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="Y2" t="n">
-        <v>28</v>
+        <v>38</v>
       </c>
       <c r="Z2" t="inlineStr"/>
       <c r="AA2" t="inlineStr"/>
@@ -697,6 +717,20 @@
           <t>2022/PALBIT Главный каталог</t>
         </is>
       </c>
+      <c r="AH2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI2" t="n">
+        <v>552.48</v>
+      </c>
+      <c r="AJ2" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="AK2" t="n">
+        <v>48553.38</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -706,7 +740,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>AVH40 DCLN L-12</t>
+          <t>AVH16 SCLC L-06</t>
         </is>
       </c>
       <c r="C3" t="inlineStr"/>
@@ -718,7 +752,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>S</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -729,17 +763,17 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>CN..1204..</t>
+          <t>CC..0602..</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>PALB_AVH:40</t>
+          <t>PALB_AVH:16</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>ISO_CN1204H</t>
+          <t>ISO_CC0602H</t>
         </is>
       </c>
       <c r="L3" t="n">
@@ -747,10 +781,10 @@
       </c>
       <c r="M3" t="inlineStr"/>
       <c r="N3" t="n">
-        <v>50</v>
+        <v>20</v>
       </c>
       <c r="O3" t="n">
-        <v>40</v>
+        <v>16</v>
       </c>
       <c r="P3" t="inlineStr"/>
       <c r="Q3" t="inlineStr">
@@ -764,7 +798,7 @@
         </is>
       </c>
       <c r="S3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="T3" t="n">
         <v>0</v>
@@ -777,10 +811,10 @@
         <v>0</v>
       </c>
       <c r="X3" t="n">
-        <v>27</v>
+        <v>11</v>
       </c>
       <c r="Y3" t="n">
-        <v>38</v>
+        <v>20</v>
       </c>
       <c r="Z3" t="inlineStr"/>
       <c r="AA3" t="inlineStr"/>
@@ -800,6 +834,20 @@
           <t>2022/PALBIT Главный каталог</t>
         </is>
       </c>
+      <c r="AH3" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI3" t="n">
+        <v>443.39</v>
+      </c>
+      <c r="AJ3" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="AK3" t="n">
+        <v>38966.27</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -809,7 +857,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>AVH40 SCLC R-12</t>
+          <t>AVH20 SCLC R-09</t>
         </is>
       </c>
       <c r="C4" t="inlineStr"/>
@@ -832,17 +880,17 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>CC..1204..</t>
+          <t>CC..09T3..</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>PALB_AVH:40</t>
+          <t>PALB_AVH:20</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>ISO_CC1204H</t>
+          <t>ISO_CC09T3H</t>
         </is>
       </c>
       <c r="L4" t="n">
@@ -850,10 +898,10 @@
       </c>
       <c r="M4" t="inlineStr"/>
       <c r="N4" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="O4" t="n">
-        <v>40</v>
+        <v>20</v>
       </c>
       <c r="P4" t="inlineStr"/>
       <c r="Q4" t="inlineStr">
@@ -880,10 +928,10 @@
         <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>27</v>
+        <v>13</v>
       </c>
       <c r="Y4" t="n">
-        <v>38</v>
+        <v>20</v>
       </c>
       <c r="Z4" t="inlineStr"/>
       <c r="AA4" t="inlineStr"/>
@@ -903,6 +951,20 @@
           <t>2022/PALBIT Главный каталог</t>
         </is>
       </c>
+      <c r="AH4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI4" t="n">
+        <v>468.97</v>
+      </c>
+      <c r="AJ4" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="AK4" t="n">
+        <v>41214.3</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -912,7 +974,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>AVH20 SCLC R-09</t>
+          <t>AVH40 DCLN R-12</t>
         </is>
       </c>
       <c r="C5" t="inlineStr"/>
@@ -924,7 +986,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>D</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -935,17 +997,17 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>CC..09T3..</t>
+          <t>CN..1204..</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>PALB_AVH:20</t>
+          <t>PALB_AVH:40</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>ISO_CC09T3H</t>
+          <t>ISO_CN1204H</t>
         </is>
       </c>
       <c r="L5" t="n">
@@ -953,10 +1015,10 @@
       </c>
       <c r="M5" t="inlineStr"/>
       <c r="N5" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="O5" t="n">
-        <v>20</v>
+        <v>40</v>
       </c>
       <c r="P5" t="inlineStr"/>
       <c r="Q5" t="inlineStr">
@@ -970,7 +1032,7 @@
         </is>
       </c>
       <c r="S5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="T5" t="n">
         <v>0</v>
@@ -983,10 +1045,10 @@
         <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>13</v>
+        <v>27</v>
       </c>
       <c r="Y5" t="n">
-        <v>20</v>
+        <v>38</v>
       </c>
       <c r="Z5" t="inlineStr"/>
       <c r="AA5" t="inlineStr"/>
@@ -1006,6 +1068,20 @@
           <t>2022/PALBIT Главный каталог</t>
         </is>
       </c>
+      <c r="AH5" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI5" t="n">
+        <v>552.48</v>
+      </c>
+      <c r="AJ5" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="AK5" t="n">
+        <v>48553.38</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -1015,7 +1091,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>AVH20 SCLC L-09</t>
+          <t>AVH40 SDUC R-11</t>
         </is>
       </c>
       <c r="C6" t="inlineStr"/>
@@ -1031,24 +1107,24 @@
         </is>
       </c>
       <c r="G6" t="n">
-        <v>95</v>
+        <v>87</v>
       </c>
       <c r="H6" t="n">
-        <v>-5</v>
+        <v>3</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>CC..09T3..</t>
+          <t>DC..11T3..</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>PALB_AVH:20</t>
+          <t>PALB_AVH:40</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>ISO_CC09T3H</t>
+          <t>ISO_DC11T3H</t>
         </is>
       </c>
       <c r="L6" t="n">
@@ -1056,20 +1132,20 @@
       </c>
       <c r="M6" t="inlineStr"/>
       <c r="N6" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="O6" t="n">
-        <v>20</v>
+        <v>40</v>
       </c>
       <c r="P6" t="inlineStr"/>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>ZX</t>
+          <t>ZXA</t>
         </is>
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>R</t>
         </is>
       </c>
       <c r="S6" t="n">
@@ -1086,10 +1162,10 @@
         <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>13</v>
+        <v>27</v>
       </c>
       <c r="Y6" t="n">
-        <v>20</v>
+        <v>32</v>
       </c>
       <c r="Z6" t="inlineStr"/>
       <c r="AA6" t="inlineStr"/>
@@ -1109,6 +1185,20 @@
           <t>2022/PALBIT Главный каталог</t>
         </is>
       </c>
+      <c r="AH6" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI6" t="n">
+        <v>528.41</v>
+      </c>
+      <c r="AJ6" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="AK6" t="n">
+        <v>46438.04</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
